--- a/data/trans_orig/IP04D$individual-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$individual-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24099</t>
+          <t>23878</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9157</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20405</t>
+          <t>20509</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22783</t>
+          <t>23655</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39019</t>
+          <t>40587</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68270</t>
+          <t>68491</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81047</t>
+          <t>80642</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65787</t>
+          <t>65683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77035</t>
+          <t>77260</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>139542</t>
+          <t>137974</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>155778</t>
+          <t>154906</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>86,75%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>102087</t>
+          <t>101991</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>130576</t>
+          <t>131071</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>129748</t>
+          <t>130325</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>163013</t>
+          <t>164286</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>241255</t>
+          <t>241641</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>285388</t>
+          <t>286775</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>318535</t>
+          <t>318040</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>347024</t>
+          <t>347120</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>330150</t>
+          <t>328877</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363415</t>
+          <t>362838</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>656887</t>
+          <t>655500</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>701020</t>
+          <t>700634</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,36%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55801</t>
+          <t>55732</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77273</t>
+          <t>77366</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66432</t>
+          <t>65836</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88860</t>
+          <t>87396</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>129258</t>
+          <t>128840</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159452</t>
+          <t>158762</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,83%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89539</t>
+          <t>89446</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>111011</t>
+          <t>111080</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83368</t>
+          <t>84832</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>105796</t>
+          <t>106392</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>179589</t>
+          <t>180279</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>209783</t>
+          <t>210201</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>62,0%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>181701</t>
+          <t>179896</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>221031</t>
+          <t>219776</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>217470</t>
+          <t>216775</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>258063</t>
+          <t>260300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>409648</t>
+          <t>406819</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>465813</t>
+          <t>467700</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>487261</t>
+          <t>488516</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>526591</t>
+          <t>528396</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>493521</t>
+          <t>491284</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>534114</t>
+          <t>534809</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>994063</t>
+          <t>992176</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1050228</t>
+          <t>1053057</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,13%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11762</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13029</t>
+          <t>13272</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>9651</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21392</t>
+          <t>21194</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46988</t>
+          <t>46986</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55156</t>
+          <t>54803</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55585</t>
+          <t>55342</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64598</t>
+          <t>64616</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105972</t>
+          <t>106170</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118390</t>
+          <t>117713</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>126201</t>
+          <t>125428</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>158013</t>
+          <t>156376</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122787</t>
+          <t>123851</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>155482</t>
+          <t>157937</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>258463</t>
+          <t>257028</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>303564</t>
+          <t>302741</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>312780</t>
+          <t>314417</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>344592</t>
+          <t>345365</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>330605</t>
+          <t>328150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363300</t>
+          <t>362236</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>653316</t>
+          <t>654139</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>698417</t>
+          <t>699852</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>73,14%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64310</t>
+          <t>64009</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85369</t>
+          <t>84826</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55903</t>
+          <t>55584</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76715</t>
+          <t>76593</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124990</t>
+          <t>126811</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153859</t>
+          <t>155986</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,82%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85269</t>
+          <t>85812</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>106328</t>
+          <t>106629</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>108595</t>
+          <t>108717</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129407</t>
+          <t>129726</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>202088</t>
+          <t>199961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>230957</t>
+          <t>229136</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,37%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>202173</t>
+          <t>203027</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>242461</t>
+          <t>242223</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>190319</t>
+          <t>193406</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>232392</t>
+          <t>234009</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>409889</t>
+          <t>405192</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>465742</t>
+          <t>463161</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>457720</t>
+          <t>457958</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>498008</t>
+          <t>497154</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>507619</t>
+          <t>506002</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>549692</t>
+          <t>546605</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>974450</t>
+          <t>977031</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1030303</t>
+          <t>1035000</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19669</t>
+          <t>20087</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10386</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26311</t>
+          <t>25759</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45711</t>
+          <t>45365</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53052</t>
+          <t>53157</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42335</t>
+          <t>41917</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55208</t>
+          <t>54818</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90371</t>
+          <t>90923</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106296</t>
+          <t>106363</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47084</t>
+          <t>45830</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74924</t>
+          <t>74335</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69586</t>
+          <t>70336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>122720</t>
+          <t>123898</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>125745</t>
+          <t>124791</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>184275</t>
+          <t>185046</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,95%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>385586</t>
+          <t>386175</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>413426</t>
+          <t>414680</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>393192</t>
+          <t>392014</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>446326</t>
+          <t>445576</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>792147</t>
+          <t>791376</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>850677</t>
+          <t>851631</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,22%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32642</t>
+          <t>32813</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50512</t>
+          <t>51484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45327</t>
+          <t>45228</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68067</t>
+          <t>68981</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82626</t>
+          <t>83882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113525</t>
+          <t>114450</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,58%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98040</t>
+          <t>97068</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>115910</t>
+          <t>115739</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>114338</t>
+          <t>113424</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137078</t>
+          <t>137177</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>217432</t>
+          <t>216507</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>248331</t>
+          <t>247075</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,65%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87022</t>
+          <t>87384</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123086</t>
+          <t>125630</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>134069</t>
+          <t>134546</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>191362</t>
+          <t>189991</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>233500</t>
+          <t>232574</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>303995</t>
+          <t>296681</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>540653</t>
+          <t>538109</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>576717</t>
+          <t>576355</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>568960</t>
+          <t>570331</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>626253</t>
+          <t>625776</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1120065</t>
+          <t>1127379</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1190560</t>
+          <t>1191486</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04D$individual-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$individual-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14301</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9220</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20805</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,59%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,14%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>17061</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11727</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23878</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>11399</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>23849</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>18,47%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,7%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>25,85%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14301</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8932</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>20509</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>16,59%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23655</t>
+          <t>23392</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40587</t>
+          <t>39951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>71891</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>65387</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>76972</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,41%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>75,86%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89,3%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>75308</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>68491</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>80642</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>68520</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>80970</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>81,53%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>74,15%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>87,3%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>71891</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>65683</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>77260</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>83,41%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>137974</t>
+          <t>138610</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>154906</t>
+          <t>155169</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,9%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>146444</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>130873</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>164082</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>29,69%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>26,54%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>33,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>115935</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>101991</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>131071</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>101829</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>132133</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>25,81%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22,71%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>146444</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>130325</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>164286</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>29,69%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>241641</t>
+          <t>242845</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>286775</t>
+          <t>286006</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>346719</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>329081</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>362290</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>70,31%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>66,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>73,46%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>481</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>333176</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>318040</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>347120</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>316978</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>347282</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>74,19%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>346719</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>328877</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>362838</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>70,31%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>655500</t>
+          <t>656269</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>700634</t>
+          <t>699430</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,23%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>493163</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>493163</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>493163</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449111</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449111</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449111</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>493163</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>493163</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>493163</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>77276</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>66874</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>87821</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>44,87%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>38,83%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>50,99%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>66912</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>55732</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>77366</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>55601</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>78105</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>40,11%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>33,41%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>46,38%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>77276</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>65836</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>87396</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>44,87%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>128840</t>
+          <t>128365</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158762</t>
+          <t>159008</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,9%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>94952</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>84407</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>105354</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>55,13%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>49,01%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>61,17%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>99900</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>89446</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>111080</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>88707</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>111211</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>59,89%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>53,62%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>66,59%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>94952</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>84832</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>106392</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>55,13%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>180279</t>
+          <t>180033</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>210201</t>
+          <t>210676</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,14%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>238021</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>217925</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>258765</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,67%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>29,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>34,43%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>287</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>199908</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>179896</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>219776</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>180444</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>219171</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>28,22%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25,4%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>31,03%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>238021</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>216775</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>260300</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>31,67%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>406819</t>
+          <t>409546</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>467700</t>
+          <t>468710</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>513563</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>492819</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>533659</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>68,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>65,57%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>71,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>734</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>508384</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>488516</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>528396</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>489121</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>527848</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>71,78%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>68,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>74,6%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>729</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>513563</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>491284</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>534809</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>68,33%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>992176</t>
+          <t>991166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1053057</t>
+          <t>1050330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>71,95%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>751584</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>751584</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>751584</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1021</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>708292</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>751584</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>751584</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>751584</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2330,67 +2330,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>7509</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4151</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13066</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10,94%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>19,04%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>6974</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3947</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11764</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3616</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11810</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>11,87%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7509</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3998</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>13272</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10,94%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9651</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21194</t>
+          <t>21154</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -2438,72 +2438,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>61105</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>55548</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>64463</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>89,06%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>80,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,95%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>51776</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>46986</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54803</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>46940</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>55134</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>88,13%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>79,98%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>61105</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>55342</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>64616</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>89,06%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106170</t>
+          <t>106210</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117713</t>
+          <t>118192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>58750</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>58750</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>58750</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>139042</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>122406</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>155984</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>28,6%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>25,18%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>32,09%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>141201</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>125428</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>156376</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>124360</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>157520</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>29,99%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>26,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>33,22%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>139042</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>123851</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>157937</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>28,6%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>257028</t>
+          <t>260779</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>302741</t>
+          <t>307851</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -2781,72 +2781,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>347045</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>330103</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>363681</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>71,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>67,91%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>74,82%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>494</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>329592</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>314417</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>345365</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>313273</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>346433</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>70,01%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>66,78%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>73,36%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>347045</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>328150</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>362236</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>71,4%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>654139</t>
+          <t>649029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>699852</t>
+          <t>696101</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>486087</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>486087</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>486087</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>470793</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>470793</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>470793</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>486087</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>486087</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>486087</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,72 +3011,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>65488</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>54703</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>76583</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>35,34%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>29,52%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>41,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>74570</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>64009</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>84826</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>64265</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>85639</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>43,7%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>65488</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>55584</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>76593</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>35,34%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126811</t>
+          <t>124278</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>155986</t>
+          <t>155758</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,76%</t>
         </is>
       </c>
     </row>
@@ -3124,72 +3124,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>119822</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>108727</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>130607</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>64,66%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>58,67%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>70,48%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>96068</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>85812</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>106629</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>84999</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>106373</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>56,3%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>50,29%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>62,49%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>119822</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>108717</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>129726</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>64,66%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>199961</t>
+          <t>200189</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>229136</t>
+          <t>231669</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>65,09%</t>
         </is>
       </c>
     </row>
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>185310</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>185310</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>185310</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>170638</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>170638</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>170638</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>185310</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>185310</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>185310</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>212039</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>193026</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>230708</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>28,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,18%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>342</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>222745</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>203027</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>242223</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>202777</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>242038</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>31,81%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>34,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>212039</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>193406</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>234009</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>28,65%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>405192</t>
+          <t>406858</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>463161</t>
+          <t>464447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,25%</t>
         </is>
       </c>
     </row>
@@ -3467,72 +3467,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>527972</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>509303</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>546985</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>71,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>68,82%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>73,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>713</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>477436</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>457958</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>497154</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>458143</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>497404</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>68,19%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>65,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>71,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>752</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>527972</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>506002</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>546605</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>71,35%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>977031</t>
+          <t>975745</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1035000</t>
+          <t>1033334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,75%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1055</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>700181</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3928,72 +3928,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11774</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6479</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18334</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,42%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>32,32%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4326</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1521</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9313</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,03%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12556</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20087</t>
+          <t>9156</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16300</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>9992</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25759</t>
+          <t>24586</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>44958</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>38398</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>50253</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>79,25%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>67,68%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,58%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>50352</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>45365</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>53157</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>92,09%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>82,97%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,22%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>49448</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41917</t>
+          <t>37602</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54818</t>
+          <t>45026</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>99800</t>
+          <t>87190</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90923</t>
+          <t>78904</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106363</t>
+          <t>93498</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,35%</t>
         </is>
       </c>
     </row>
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4271,72 +4271,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>80088</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>64494</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>109176</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16,86%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,58%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>60225</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>45830</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>74335</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13,08%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,95%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,14%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87852</t>
+          <t>60714</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70336</t>
+          <t>49184</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123898</t>
+          <t>74092</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>148077</t>
+          <t>140802</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>124791</t>
+          <t>121082</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>185046</t>
+          <t>170214</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -4384,72 +4384,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>394974</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>365886</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>410568</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>83,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,42%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>556</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>400285</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>386175</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>414680</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>86,92%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,86%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>428060</t>
+          <t>371734</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>392014</t>
+          <t>358356</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>445576</t>
+          <t>383264</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>828345</t>
+          <t>766708</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>791376</t>
+          <t>737296</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>851631</t>
+          <t>786428</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>86,66%</t>
         </is>
       </c>
     </row>
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475062</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475062</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475062</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>515912</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>515912</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>515912</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>976422</t>
+          <t>907510</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>976422</t>
+          <t>907510</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>976422</t>
+          <t>907510</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4614,72 +4614,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>52057</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>40846</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>62356</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>31,09%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,39%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>37,24%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>41463</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>32813</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>51484</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>27,91%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>55908</t>
+          <t>41121</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45228</t>
+          <t>32393</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68981</t>
+          <t>50752</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,32 +4689,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>97371</t>
+          <t>93178</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83882</t>
+          <t>79861</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114450</t>
+          <t>106927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -4727,72 +4727,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>115405</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>105106</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>126616</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>68,91%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>62,76%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>75,61%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>107089</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>97068</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>115739</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>72,09%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>65,34%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>77,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>126497</t>
+          <t>107780</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113424</t>
+          <t>98149</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137177</t>
+          <t>116508</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>233586</t>
+          <t>223184</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>216507</t>
+          <t>209435</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>247075</t>
+          <t>236501</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,76%</t>
         </is>
       </c>
     </row>
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>148552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>148552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>148552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148901</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148901</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148901</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>316362</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>316362</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>316362</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4957,72 +4957,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>143920</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>123615</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>172157</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>20,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17,68%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>106014</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>87384</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>125630</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>15,97%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>156315</t>
+          <t>106361</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>134546</t>
+          <t>90882</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>189991</t>
+          <t>122211</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>262330</t>
+          <t>250281</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>232574</t>
+          <t>222521</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>296681</t>
+          <t>280327</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -5070,72 +5070,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>555336</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>527099</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>575641</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>79,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>75,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>82,32%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>788</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>557725</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>538109</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>576355</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>84,03%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>86,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>604007</t>
+          <t>521745</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>570331</t>
+          <t>505895</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>625776</t>
+          <t>537224</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1161730</t>
+          <t>1077081</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1127379</t>
+          <t>1047035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1191486</t>
+          <t>1104841</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,24%</t>
         </is>
       </c>
     </row>
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663739</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663739</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663739</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628106</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628106</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628106</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1424060</t>
+          <t>1327362</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1424060</t>
+          <t>1327362</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1424060</t>
+          <t>1327362</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
